--- a/Table/TableAsset/TB_Weapon.xlsx
+++ b/Table/TableAsset/TB_Weapon.xlsx
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>10</v>
@@ -715,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>5</v>
+        <v>8.9</v>
       </c>
       <c r="S2" s="4" t="n"/>
     </row>
@@ -760,7 +760,7 @@
         <v>5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>8</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="S3" s="4" t="n"/>
     </row>
@@ -831,7 +831,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5" t="n">
         <v>8</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>3</v>
+        <v>5.8</v>
       </c>
       <c r="S4" s="4" t="n"/>
     </row>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K5" s="6" t="n">
         <v>8</v>
@@ -928,7 +928,7 @@
         <v>0</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S5" s="4" t="n"/>
     </row>
@@ -973,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>8</v>
@@ -999,7 +999,7 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S6" s="4" t="n"/>
     </row>
@@ -1044,7 +1044,7 @@
         <v>3</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K7" s="6" t="n">
         <v>8</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="S7" s="4" t="n"/>
     </row>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>8</v>
@@ -1141,7 +1141,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>8</v>
+        <v>13.9</v>
       </c>
       <c r="S8" s="4" t="n"/>
     </row>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>8</v>
@@ -1212,7 +1212,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="S9" s="4" t="n"/>
     </row>

--- a/Table/TableAsset/TB_Weapon.xlsx
+++ b/Table/TableAsset/TB_Weapon.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="TB_Weapon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -68,6 +67,13 @@
       <family val="3"/>
       <color rgb="FF37474F"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -176,7 +182,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -539,8 +545,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:X41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.9"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
@@ -647,6 +653,31 @@
           <t>damage_per_level</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>etc_comment1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>etc_comment2</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>etc_comment3</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>etc_comment4</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>etc_comment5</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -717,7 +748,32 @@
       <c r="R2" s="3" t="n">
         <v>8.9</v>
       </c>
-      <c r="S2" s="4" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>레벨당 데미지 증가</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -780,7 +836,7 @@
         <v>0.3</v>
       </c>
       <c r="P3" s="3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="Q3" s="3" t="n">
         <v>0</v>
@@ -788,7 +844,32 @@
       <c r="R3" s="3" t="n">
         <v>1.6</v>
       </c>
-      <c r="S3" s="4" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>감속 비율 (50=50%)</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>감속 지속시간 (초)</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>기본 웅덩이 반경</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>레벨당 반경 증가량</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -859,7 +940,32 @@
       <c r="R4" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="S4" s="4" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>회전 속도 (도/초)</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>궤도 반경</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>타격 간격 (초)</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>(미사용, 개수=레벨)</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -930,7 +1036,32 @@
       <c r="R5" s="3" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="S5" s="4" t="n"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>기본 타격 인원수</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>레벨당 추가 인원 (+1)</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -949,7 +1080,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -999,9 +1130,34 @@
         <v>0</v>
       </c>
       <c r="R6" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="S6" s="4" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>기본 스턴 지속시간 (초)</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>기본 반경</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>레벨당 반경 증가량</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1020,7 +1176,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -1055,7 +1211,7 @@
         </is>
       </c>
       <c r="M7" s="8" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N7" s="8" t="n">
         <v>2</v>
@@ -1064,15 +1220,40 @@
         <v>0.3</v>
       </c>
       <c r="P7" s="8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" s="8" t="n">
         <v>0</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="S7" s="4" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>기본 화염 지속시간 (초)</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>기본 화염 반경</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>레벨당 반경 증가량</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>화염 오프셋 Y</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1143,7 +1324,32 @@
       <c r="R8" s="3" t="n">
         <v>13.9</v>
       </c>
-      <c r="S8" s="4" t="n"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>기본 레이저 줄기 수</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>레벨당 레이저 추가 (+1)</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1214,7 +1420,32 @@
       <c r="R9" s="3" t="n">
         <v>17.8</v>
       </c>
-      <c r="S9" s="4" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>기본 미사일 수</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>레벨당 미사일 추가 (+1)</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>(미사용)</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n"/>
@@ -1235,7 +1466,7 @@
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
+      <c r="X10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
@@ -1268,7 +1499,7 @@
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="n"/>
+      <c r="X11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1301,7 +1532,7 @@
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
+      <c r="X12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1334,7 +1565,7 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
+      <c r="X13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -1367,7 +1598,7 @@
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
+      <c r="X14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -1400,7 +1631,7 @@
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
+      <c r="X15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -1433,7 +1664,7 @@
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
+      <c r="X16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -1466,9 +1697,9 @@
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n"/>
-    </row>
-    <row r="18">
+      <c r="X17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="47.25" customHeight="1">
       <c r="A18" s="10" t="inlineStr">
         <is>
           <t>weapon_type</t>
@@ -1499,7 +1730,7 @@
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
+      <c r="X18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -1532,7 +1763,7 @@
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
+      <c r="X19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
@@ -1565,7 +1796,7 @@
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
-      <c r="S20" s="4" t="n"/>
+      <c r="X20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1598,7 +1829,7 @@
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
+      <c r="X21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
@@ -1631,7 +1862,7 @@
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
       <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
+      <c r="X22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1664,9 +1895,9 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
-    </row>
-    <row r="24">
+      <c r="X23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="126" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
           <t>etc_value1</t>
@@ -1704,9 +1935,9 @@
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n"/>
-    </row>
-    <row r="25">
+      <c r="X24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="126" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
           <t>etc_value2</t>
@@ -1744,9 +1975,9 @@
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
-    </row>
-    <row r="26">
+      <c r="X25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="126" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
           <t>etc_value3</t>
@@ -1784,7 +2015,7 @@
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
+      <c r="X26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
@@ -1817,7 +2048,7 @@
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
-      <c r="S27" s="4" t="n"/>
+      <c r="X27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
@@ -1850,7 +2081,7 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
+      <c r="X28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
@@ -1883,7 +2114,7 @@
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="n"/>
       <c r="R29" s="4" t="n"/>
-      <c r="S29" s="4" t="n"/>
+      <c r="X29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
@@ -1904,7 +2135,7 @@
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
-      <c r="S30" s="4" t="n"/>
+      <c r="X30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
@@ -1925,7 +2156,7 @@
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
-      <c r="S31" s="4" t="n"/>
+      <c r="X31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
@@ -1946,7 +2177,7 @@
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="n"/>
+      <c r="X32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
@@ -1967,7 +2198,7 @@
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
-      <c r="S33" s="4" t="n"/>
+      <c r="X33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
@@ -1988,7 +2219,7 @@
       <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
+      <c r="X34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
@@ -2009,7 +2240,7 @@
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
-      <c r="S35" s="4" t="n"/>
+      <c r="X35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
@@ -2030,7 +2261,7 @@
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
+      <c r="X36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
@@ -2051,7 +2282,7 @@
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
-      <c r="S37" s="4" t="n"/>
+      <c r="X37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
@@ -2072,7 +2303,7 @@
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
+      <c r="X38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
@@ -2093,7 +2324,7 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="n"/>
+      <c r="X39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
@@ -2114,7 +2345,7 @@
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
-      <c r="S40" s="4" t="n"/>
+      <c r="X40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n"/>
@@ -2135,7 +2366,7 @@
       <c r="P41" s="4" t="n"/>
       <c r="Q41" s="4" t="n"/>
       <c r="R41" s="4" t="n"/>
-      <c r="S41" s="4" t="n"/>
+      <c r="X41" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
